--- a/examples/hkex-2025/deliverables/workbook.xlsx
+++ b/examples/hkex-2025/deliverables/workbook.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Facts!$A$1:$R$95</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Findings!$A$1:$I$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Procedures!$A$1:$J$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Readme!$A$1:$B$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Readme!$A$1:$B$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Reconciliations!$A$1:$J$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Requests!$A$1:$F$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sources!$A$1:$F$4</definedName>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1915" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1917" uniqueCount="585">
   <si>
     <t>字段 / field</t>
   </si>
@@ -74,6 +74,12 @@
     <t>HKFRS</t>
   </si>
   <si>
+    <t>方法与适用范围</t>
+  </si>
+  <si>
+    <t>SKILL、analysis-program、accounting-and-audit、financial-institutions、workpaper契约</t>
+  </si>
+  <si>
     <t>单位</t>
   </si>
   <si>
@@ -110,7 +116,7 @@
     <t>未取得服务级规则簿、PFMI定量披露、日内付款数据、总部购置合同及CGU完整估值模型。</t>
   </si>
   <si>
-    <t>已取得FCA最终文书及独立可持续报告，并定向核读风险、治理及有限保证范围；未执行网络、气候模型或整改运行测试。</t>
+    <t>已取得FCA最终文书及独立可持续报告，并接读保证声明并入的附录A；HKQAA有限保证不评价ESG政策执行有效性或全面模型适当性。本次未执行网络、气候模型或整改运行测试。</t>
   </si>
   <si>
     <t>来源 annual, sr 的正式公布日期未核验；不得据此证明在信息截止日前已公开。当前披露内容可以继续分析，历史时点结论须补充公告时间证据。</t>
@@ -863,7 +869,7 @@
     <t>营业收入同比增量</t>
   </si>
   <si>
-    <t>HKD × 1000000</t>
+    <t>百万HKD</t>
   </si>
   <si>
     <t>totalgain</t>
@@ -1286,7 +1292,7 @@
     <t>ea0deef0b3f3a0d31c01d7936d60a652e4a3b9a6dd41b7d5351a80fba6b4af5f</t>
   </si>
   <si>
-    <t>已取得76页原件；读取PDF42-43、56-58、71-72页，首次公告日未单独核验。</t>
+    <t>已取得76页原件；读取PDF42-43、56-58、71-74页，含保证声明及其明确并入的附录A；首次公告日未单独核验。</t>
   </si>
   <si>
     <t>来源</t>
@@ -1406,13 +1412,13 @@
     <t>e_sr</t>
   </si>
   <si>
-    <t>PDF42-43、56-58、71-72；印刷40-41、54-56、69-70</t>
-  </si>
-  <si>
-    <t>披露网络独立专家验证、数据中心ISO27001、定期演练、2025第三方隐私复核；风灾期间交易结算正常是正面执行实例。气候评估覆盖17个自有及租用站点，比较NGFS路径并连接交易收入、资产损害/能源成本；存在公司表现不变及技术不变等假设。HKQAA声明为ISAE3000有限保证，非本次网络运行或气候模型验证。</t>
-  </si>
-  <si>
-    <t>公司独立报告与第三方有限保证原件；管理层模型结果与保证范围均保留限制</t>
+    <t>PDF42-43、56-58、71-74；印刷40-41、54-56、69-72；保证声明及附录A</t>
+  </si>
+  <si>
+    <t>披露网络独立专家验证、数据中心ISO27001、定期演练、2025第三方隐私复核；风灾期间交易结算正常是正面执行实例。气候评估覆盖17个自有及租用站点，比较NGFS路径并连接交易收入、资产损害/能源成本；存在公司表现不变及技术不变等假设。HKQAA声明称程序参照ISAE3000，以有限保证评价2025年度披露是否按ESG Reporting Code编制，并参考GRI。正文明确并入附录A：范围限于数据向披露的转录或转换，不评价ESG政策及实践的执行或有效性，不全面评价管理层判断、假设或估计技术；报告期外信息排除。该保证不是本次网络运行或气候模型验证。</t>
+  </si>
+  <si>
+    <t>公司披露与HKQAA有限保证原件；外部保证依赖公司提供资料及系统/模型假设，不把公司演练实例当作保证方运行测试，亦不证明气候模型假设已获全面验证</t>
   </si>
   <si>
     <t>问题</t>
@@ -1442,7 +1448,7 @@
     <t>盈利改善是否只来自利率和投资收益？</t>
   </si>
   <si>
-    <t>营业收入同比36.89%，集团净利润同比35.59%。营业收入增量6,399.00 HKD × 1000000占收入及其他收益增量的94.28%；现金分部占公司定义EBITDA增量80.26%。</t>
+    <t>营业收入同比36.89%，集团净利润同比35.59%。营业收入增量6,399.00 百万HKD占收入及其他收益增量的94.28%；现金分部占公司定义EBITDA增量80.26%。</t>
   </si>
   <si>
     <t>牌照及互联互通网络将活跃交易转化为交易、清算和存管收入；量增同时扩大清算资源和IT容量需求。不能把所有收入机械乘股票ADT。</t>
@@ -1467,7 +1473,7 @@
     <t>CFO与会员资金能否直接解释为可分配现金？</t>
   </si>
   <si>
-    <t>逐行桥得到主要经营现金19,855.00 HKD × 1000000、HKAS7 CFO25,627.00 HKD × 1000000；其中外部基金赎回为5,772.00 HKD × 1000000。现金流量表现金19,353.00 HKD × 1000000与资产负债表现金182,724.00 HKD × 1000000是不同范围。</t>
+    <t>逐行桥得到主要经营现金19,855.00 百万HKD、HKAS7 CFO25,627.00 百万HKD；其中外部基金赎回为5,772.00 百万HKD。现金流量表现金19,353.00 百万HKD与资产负债表现金182,724.00 百万HKD是不同范围。</t>
   </si>
   <si>
     <t>附注披露的会员配对资金通过经营现金桥但不可用于其他活动；清算与公司不同用途资源不能混用。其他负债增加与应收增加只能解释原合计行，未分解前不能称供应商占款。</t>
@@ -1489,7 +1495,7 @@
     <t>资源总额能否证明清算风险已覆盖？</t>
   </si>
   <si>
-    <t>保证金资产重建269,243.00 HKD × 1000000对应义务269,243.00 HKD × 1000000；清算基金净资产35,796.00 HKD × 1000000与披露一致。</t>
+    <t>保证金资产重建269,243.00 百万HKD对应义务269,243.00 百万HKD；清算基金净资产35,796.00 百万HKD与披露一致。</t>
   </si>
   <si>
     <t>资产用途、期限与服务级法律顺序决定可用性；非现金会员抵押并未上表，跨CCP及币种资金不能简单互抵；年度账面闭合不回答日内支付和极端平仓损失。</t>
@@ -1513,10 +1519,10 @@
     <t>股东分配能否只读现金流表？</t>
   </si>
   <si>
-    <t>全权益滚动58,729.00 HKD × 1000000、资产负债差58,729.00 HKD × 1000000与集团权益58,729.00 HKD × 1000000一致；看跌期权债务重建398.00 HKD × 1000000。</t>
-  </si>
-  <si>
-    <t>非控股分配59.00 HKD × 1000000现金流出同时降低看跌期权负债，并在权益内把NCI转至归母储备，集团权益该行净零。宣告分配与实付股息另列，避免把权益增减全部理解成现金。</t>
+    <t>全权益滚动58,729.00 百万HKD、资产负债差58,729.00 百万HKD与集团权益58,729.00 百万HKD一致；看跌期权债务重建398.00 百万HKD。</t>
+  </si>
+  <si>
+    <t>非控股分配59.00 百万HKD现金流出同时降低看跌期权负债，并在权益内把NCI转至归母储备，集团权益该行净零。宣告分配与实付股息另列，避免把权益增减全部理解成现金。</t>
   </si>
   <si>
     <t>e_equity, e_bs</t>
@@ -1534,7 +1540,7 @@
     <t>资产估计是否与业务战略一致？</t>
   </si>
   <si>
-    <t>商誉重建13,274.00 HKD × 1000000，本年减值55.00 HKD × 1000000；软件净值重建4,341.00 HKD × 1000000。BayConnect协同预期下调已有会计后果，不能将减值全当无关紧要的非现金项目。</t>
+    <t>商誉重建13,274.00 百万HKD，本年减值55.00 百万HKD；软件净值重建4,341.00 百万HKD。BayConnect协同预期下调已有会计后果，不能将减值全当无关紧要的非现金项目。</t>
   </si>
   <si>
     <t>深圳技术中心定位改变降低BayConnect协同；LME等商品CGU仍承载主要商誉和商标，管理层提高利润率假设是增长解释，也是应挑战的估计输入。软件资本化与收入系统依赖连接未来摊销及运营韧性。</t>
@@ -1556,10 +1562,10 @@
     <t>当年高经营现金是否足够说明资本配置无约束？</t>
   </si>
   <si>
-    <t>主要经营现金减总部和其他长期经营资产付款为14,974.00 HKD × 1000000，再减归母股息实付剩1,252.00 HKD × 1000000；尚有总部已签承诺3,424.00 HKD × 1000000及其他资本安排。</t>
-  </si>
-  <si>
-    <t>该观察未扣联营投资、奖励股份、租赁和其他资金变动；总部ROU/固定资产确认与付款及未来承诺不同步，不能把会计新增当现金支出。母公司现金2,870.00 HKD × 1000000也不同于集团资金。</t>
+    <t>主要经营现金减总部和其他长期经营资产付款为14,974.00 百万HKD，再减归母股息实付剩1,252.00 百万HKD；尚有总部已签承诺3,424.00 百万HKD及其他资本安排。</t>
+  </si>
+  <si>
+    <t>该观察未扣联营投资、奖励股份、租赁和其他资金变动；总部ROU/固定资产确认与付款及未来承诺不同步，不能把会计新增当现金支出。母公司现金2,870.00 百万HKD也不同于集团资金。</t>
   </si>
   <si>
     <t>e_capital, e_cf, e_parent</t>
@@ -1577,7 +1583,7 @@
     <t>税后增速与税前增长为何不同？</t>
   </si>
   <si>
-    <t>税前利润同比42.45%，净利润同比35.59%；本年有效税率15.70%。最低补足税701.00 HKD × 1000000占所得税费用增量43.19%。</t>
+    <t>税前利润同比42.45%，净利润同比35.59%；本年有效税率15.70%。最低补足税701.00 百万HKD占所得税费用增量43.19%。</t>
   </si>
   <si>
     <t>最低税有明确本期税额；英国当期税抵扣与递延税相抵，不能只引用当期税利好。税费和实付税不同，未付税还影响未来现金。</t>
@@ -1620,10 +1626,10 @@
     <t>治理叙述是否已经连接业务和会计后果？</t>
   </si>
   <si>
-    <t>补充公开报告已取得。风灾中交易结算正常、网络演练和第三方隐私复核为积极证据；极端天气和网络中断仍通过交易收入、清算付款及资产/运营成本传导。</t>
-  </si>
-  <si>
-    <t>可持续报告已把场景连接站点、收入与费用，不能重复请求整份公开报告。其模型的企业表现和技术不变假设需要挑战；有限保证不替代本次关键系统运行和模型复算。</t>
+    <t>补充公开报告已取得。风灾中交易结算正常、网络演练和第三方隐私复核为积极披露证据；极端天气和网络中断仍通过交易收入、清算付款及资产/运营成本传导。HKQAA有限保证不覆盖ESG执行有效性或全面模型适当性。</t>
+  </si>
+  <si>
+    <t>可持续报告已把场景连接站点、收入与费用，不能重复请求整份公开报告。附录A将保证限制为披露数据的转录或转换，排除ESG执行效果且不全面评价判断、假设及估计技术，不能凭该保证关闭运行或模型风险。本次也未测试关键系统或复算气候模型；企业表现和技术不变假设仍需挑战。</t>
   </si>
   <si>
     <t>e_sr, e_fca</t>
@@ -1670,7 +1676,7 @@
   </si>
   <si>
     <t>从带表头原页定位并记录所选行。
-逐项执行：19,005.00 HKD × 1000000、19,855.00 HKD × 1000000、25,627.00 HKD × 1000000、19,353.00 HKD × 1000000</t>
+逐项执行：19,005.00 百万HKD、19,855.00 百万HKD、25,627.00 百万HKD、19,353.00 百万HKD</t>
   </si>
   <si>
     <t>performed</t>
@@ -1689,7 +1695,7 @@
   </si>
   <si>
     <t>从带表头原页定位并记录所选行。
-逐项执行：58,729.00 HKD × 1000000、398.00 HKD × 1000000、58,729.00 HKD × 1000000</t>
+逐项执行：58,729.00 百万HKD、398.00 百万HKD、58,729.00 百万HKD</t>
   </si>
   <si>
     <t>本次核对权益全列原页并复算，残差零；未执行权益和期权交易真实性测试。</t>
@@ -1702,7 +1708,7 @@
   </si>
   <si>
     <t>从带表头原页定位并记录所选行。
-逐项执行：13,274.00 HKD × 1000000、4,341.00 HKD × 1000000</t>
+逐项执行：13,274.00 百万HKD、4,341.00 百万HKD</t>
   </si>
   <si>
     <t>本次复算商誉、软件净值滚动，残差零；未执行CGU模型验证。</t>
@@ -1715,7 +1721,7 @@
   </si>
   <si>
     <t>从带表头原页定位并记录所选行。
-逐项执行：269,243.00 HKD × 1000000、35,796.00 HKD × 1000000</t>
+逐项执行：269,243.00 百万HKD、35,796.00 百万HKD</t>
   </si>
   <si>
     <t>本次复算保证金及清算基金资产义务勾稽，残差零；未验证违约瀑布与日内压力。</t>
@@ -1787,7 +1793,7 @@
     <t>关键收费/清算系统控制运行样本、事故升级日志和整改关闭测试；已披露气候模型的站点假设及原始结果</t>
   </si>
   <si>
-    <t>FCA最终文书及独立可持续报告已经取得，剩余是运行与模型证据；不再请求公开报告本身。</t>
+    <t>FCA最终文书及独立可持续报告含保证附录已经取得；原保证不覆盖执行效果或全面模型适当性，剩余是具体运行与模型证据，不再请求公开报告本身。</t>
   </si>
   <si>
     <t>技术风险与合规负责人</t>
@@ -2154,7 +2160,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
@@ -2169,7 +2175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -2177,7 +2183,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" ht="18" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -2185,7 +2191,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" ht="18" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -2193,7 +2199,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" ht="18" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -2201,7 +2207,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" ht="18" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2209,7 +2215,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" ht="18" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -2217,7 +2223,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" ht="18" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -2225,7 +2231,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" ht="18" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -2233,7 +2239,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" ht="33" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -2241,7 +2247,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" ht="18" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -2249,40 +2255,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" ht="18" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="18" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="B13" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="18" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="33" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="33" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B15"/>
+  <autoFilter ref="A1:B16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
 </worksheet>
@@ -2298,69 +2312,69 @@
   <sheetData>
     <row r="1" spans="1:18" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2" s="2">
         <v>23745</v>
@@ -2373,47 +2387,47 @@
         <v>23745000000.0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R2" s="2"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D3" s="2">
         <v>17346</v>
@@ -2426,47 +2440,47 @@
         <v>17346000000.0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R3" s="2"/>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D4" s="2">
         <v>29161</v>
@@ -2479,47 +2493,47 @@
         <v>29161000000.0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R4" s="2"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5" s="2">
         <v>22374</v>
@@ -2532,47 +2546,47 @@
         <v>22374000000.0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R5" s="2"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6" s="2">
         <v>5111</v>
@@ -2585,47 +2599,47 @@
         <v>5111000000.0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P6" s="2"/>
       <c r="Q6" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="R6" s="2"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D7" s="2">
         <v>4927</v>
@@ -2638,47 +2652,47 @@
         <v>4927000000.0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="R7" s="2"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8" s="2">
         <v>21158</v>
@@ -2691,47 +2705,47 @@
         <v>21158000000.0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="R8" s="2"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="C9" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D9" s="2">
         <v>14853</v>
@@ -2744,47 +2758,47 @@
         <v>14853000000.0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="R9" s="2"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D10" s="2">
         <v>3321</v>
@@ -2797,47 +2811,47 @@
         <v>3321000000.0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P10" s="2"/>
       <c r="Q10" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="R10" s="2"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="C11" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D11" s="2">
         <v>1698</v>
@@ -2850,47 +2864,47 @@
         <v>1698000000.0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P11" s="2"/>
       <c r="Q11" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="R11" s="2"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D12" s="2">
         <v>17837</v>
@@ -2903,47 +2917,47 @@
         <v>17837000000.0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P12" s="2"/>
       <c r="Q12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R12" s="2"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13" s="2">
         <v>13155</v>
@@ -2956,47 +2970,47 @@
         <v>13155000000.0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P13" s="2"/>
       <c r="Q13" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R13" s="2"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" s="2">
         <v>13398</v>
@@ -3009,47 +3023,47 @@
         <v>13398000000.0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P14" s="2"/>
       <c r="Q14" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R14" s="2"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D15" s="2">
         <v>8169</v>
@@ -3062,47 +3076,47 @@
         <v>8169000000.0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P15" s="2"/>
       <c r="Q15" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R15" s="2"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D16" s="2">
         <v>22796</v>
@@ -3115,47 +3129,47 @@
         <v>22796000000.0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P16" s="2"/>
       <c r="Q16" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="R16" s="2"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="C17" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D17" s="2">
         <v>16281</v>
@@ -3168,47 +3182,47 @@
         <v>16281000000.0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P17" s="2"/>
       <c r="Q17" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="R17" s="2"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D18" s="2">
         <v>-5111</v>
@@ -3221,47 +3235,47 @@
         <v>-5111000000.0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="R18" s="2"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="D19" s="2">
         <v>94</v>
@@ -3274,47 +3288,47 @@
         <v>94000000.0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P19" s="2"/>
       <c r="Q19" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="R19" s="2"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D20" s="2">
         <v>-76</v>
@@ -3327,47 +3341,47 @@
         <v>-76000000.0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P20" s="2"/>
       <c r="Q20" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="R20" s="2"/>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D21" s="2">
         <v>96</v>
@@ -3380,47 +3394,47 @@
         <v>96000000.0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P21" s="2"/>
       <c r="Q21" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="R21" s="2"/>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D22" s="2">
         <v>1568</v>
@@ -3433,47 +3447,47 @@
         <v>1568000000.0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P22" s="2"/>
       <c r="Q22" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="R22" s="2"/>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D23" s="2">
         <v>361</v>
@@ -3486,47 +3500,47 @@
         <v>361000000.0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P23" s="2"/>
       <c r="Q23" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="R23" s="2"/>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D24" s="2">
         <v>-26</v>
@@ -3539,47 +3553,47 @@
         <v>-26000000.0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P24" s="2"/>
       <c r="Q24" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="R24" s="2"/>
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D25" s="2">
         <v>1</v>
@@ -3592,47 +3606,47 @@
         <v>1000000.0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P25" s="2"/>
       <c r="Q25" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="R25" s="2"/>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D26" s="2">
         <v>-80198</v>
@@ -3645,47 +3659,47 @@
         <v>-80198000000.0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P26" s="2"/>
       <c r="Q26" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R26" s="2"/>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D27" s="2">
         <v>80386</v>
@@ -3698,47 +3712,47 @@
         <v>80386000000.0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P27" s="2"/>
       <c r="Q27" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="R27" s="2"/>
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D28" s="2">
         <v>-7073</v>
@@ -3751,47 +3765,47 @@
         <v>-7073000000.0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P28" s="2"/>
       <c r="Q28" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="R28" s="2"/>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D29" s="2">
         <v>6866</v>
@@ -3804,47 +3818,47 @@
         <v>6866000000.0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P29" s="2"/>
       <c r="Q29" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="R29" s="2"/>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D30" s="2">
         <v>-374</v>
@@ -3857,47 +3871,47 @@
         <v>-374000000.0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="R30" s="2"/>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D31" s="2">
         <v>-196</v>
@@ -3910,47 +3924,47 @@
         <v>-196000000.0</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P31" s="2"/>
       <c r="Q31" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="R31" s="2"/>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D32" s="2">
         <v>-145</v>
@@ -3963,47 +3977,47 @@
         <v>-145000000.0</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P32" s="2"/>
       <c r="Q32" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="R32" s="2"/>
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D33" s="2">
         <v>-11679</v>
@@ -4016,47 +4030,47 @@
         <v>-11679000000.0</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P33" s="2"/>
       <c r="Q33" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="R33" s="2"/>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D34" s="2">
         <v>13353</v>
@@ -4069,47 +4083,47 @@
         <v>13353000000.0</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P34" s="2"/>
       <c r="Q34" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="R34" s="2"/>
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D35" s="2">
         <v>19005</v>
@@ -4122,47 +4136,47 @@
         <v>19005000000.0</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P35" s="2"/>
       <c r="Q35" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="R35" s="2"/>
     </row>
     <row r="36" spans="1:18">
       <c r="A36" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D36" s="2">
         <v>7519</v>
@@ -4175,47 +4189,47 @@
         <v>7519000000.0</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P36" s="2"/>
       <c r="Q36" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="R36" s="2"/>
     </row>
     <row r="37" spans="1:18">
       <c r="A37" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D37" s="2">
         <v>-4626</v>
@@ -4228,47 +4242,47 @@
         <v>-4626000000.0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P37" s="2"/>
       <c r="Q37" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R37" s="2"/>
     </row>
     <row r="38" spans="1:18">
       <c r="A38" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D38" s="2">
         <v>-510</v>
@@ -4281,47 +4295,47 @@
         <v>-510000000.0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P38" s="2"/>
       <c r="Q38" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="R38" s="2"/>
     </row>
     <row r="39" spans="1:18">
       <c r="A39" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D39" s="2">
         <v>-1533</v>
@@ -4334,47 +4348,47 @@
         <v>-1533000000.0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P39" s="2"/>
       <c r="Q39" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="R39" s="2"/>
     </row>
     <row r="40" spans="1:18">
       <c r="A40" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D40" s="2">
         <v>19855</v>
@@ -4387,47 +4401,47 @@
         <v>19855000000.0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P40" s="2"/>
       <c r="Q40" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="R40" s="2"/>
     </row>
     <row r="41" spans="1:18">
       <c r="A41" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D41" s="2">
         <v>5772</v>
@@ -4440,47 +4454,47 @@
         <v>5772000000.0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P41" s="2"/>
       <c r="Q41" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="R41" s="2"/>
     </row>
     <row r="42" spans="1:18">
       <c r="A42" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D42" s="2">
         <v>25627</v>
@@ -4493,47 +4507,47 @@
         <v>25627000000.0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P42" s="2"/>
       <c r="Q42" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="R42" s="2"/>
     </row>
     <row r="43" spans="1:18">
       <c r="A43" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D43" s="2">
         <v>-5565</v>
@@ -4546,47 +4560,47 @@
         <v>-5565000000.0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P43" s="2"/>
       <c r="Q43" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="R43" s="2"/>
     </row>
     <row r="44" spans="1:18">
       <c r="A44" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D44" s="2">
         <v>-14635</v>
@@ -4599,47 +4613,47 @@
         <v>-14635000000.0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P44" s="2"/>
       <c r="Q44" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="R44" s="2"/>
     </row>
     <row r="45" spans="1:18">
       <c r="A45" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D45" s="2">
         <v>16</v>
@@ -4652,47 +4666,47 @@
         <v>16000000.0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P45" s="2"/>
       <c r="Q45" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="R45" s="2"/>
     </row>
     <row r="46" spans="1:18">
       <c r="A46" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D46" s="2">
         <v>3148</v>
@@ -4705,47 +4719,47 @@
         <v>3148000000.0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P46" s="2"/>
       <c r="Q46" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="R46" s="2"/>
     </row>
     <row r="47" spans="1:18">
       <c r="A47" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D47" s="2">
         <v>1733</v>
@@ -4758,47 +4772,47 @@
         <v>1733000000.0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P47" s="2"/>
       <c r="Q47" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="R47" s="2"/>
     </row>
     <row r="48" spans="1:18">
       <c r="A48" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D48" s="2">
         <v>13722</v>
@@ -4811,47 +4825,47 @@
         <v>13722000000.0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P48" s="2"/>
       <c r="Q48" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="R48" s="2"/>
     </row>
     <row r="49" spans="1:18">
       <c r="A49" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D49" s="2">
         <v>13910</v>
@@ -4864,45 +4878,45 @@
         <v>13910000000.0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K49" s="2"/>
       <c r="L49" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P49" s="2"/>
       <c r="Q49" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="R49" s="2"/>
     </row>
     <row r="50" spans="1:18">
       <c r="A50" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="D50" s="2">
         <v>19353</v>
@@ -4915,45 +4929,45 @@
         <v>19353000000.0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K50" s="2"/>
       <c r="L50" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P50" s="2"/>
       <c r="Q50" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R50" s="2"/>
     </row>
     <row r="51" spans="1:18">
       <c r="A51" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D51" s="2">
         <v>182724</v>
@@ -4966,45 +4980,45 @@
         <v>182724000000.0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K51" s="2"/>
       <c r="L51" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P51" s="2"/>
       <c r="Q51" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="R51" s="2"/>
     </row>
     <row r="52" spans="1:18">
       <c r="A52" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D52" s="2">
         <v>2549</v>
@@ -5017,45 +5031,45 @@
         <v>2549000000.0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K52" s="2"/>
       <c r="L52" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P52" s="2"/>
       <c r="Q52" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="R52" s="2"/>
     </row>
     <row r="53" spans="1:18">
       <c r="A53" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D53" s="2">
         <v>20676</v>
@@ -5068,45 +5082,45 @@
         <v>20676000000.0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K53" s="2"/>
       <c r="L53" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P53" s="2"/>
       <c r="Q53" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="R53" s="2"/>
     </row>
     <row r="54" spans="1:18">
       <c r="A54" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D54" s="2">
         <v>130052</v>
@@ -5119,45 +5133,45 @@
         <v>130052000000.0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K54" s="2"/>
       <c r="L54" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P54" s="2"/>
       <c r="Q54" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="R54" s="2"/>
     </row>
     <row r="55" spans="1:18">
       <c r="A55" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D55" s="2">
         <v>29447</v>
@@ -5170,45 +5184,45 @@
         <v>29447000000.0</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K55" s="2"/>
       <c r="L55" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O55" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P55" s="2"/>
       <c r="Q55" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="R55" s="2"/>
     </row>
     <row r="56" spans="1:18">
       <c r="A56" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D56" s="2">
         <v>1323</v>
@@ -5221,45 +5235,45 @@
         <v>1323000000.0</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K56" s="2"/>
       <c r="L56" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P56" s="2"/>
       <c r="Q56" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="R56" s="2"/>
     </row>
     <row r="57" spans="1:18">
       <c r="A57" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D57" s="2">
         <v>48327</v>
@@ -5272,45 +5286,45 @@
         <v>48327000000.0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K57" s="2"/>
       <c r="L57" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P57" s="2"/>
       <c r="Q57" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="R57" s="2"/>
     </row>
     <row r="58" spans="1:18">
       <c r="A58" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="D58" s="2">
         <v>69176</v>
@@ -5323,45 +5337,45 @@
         <v>69176000000.0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K58" s="2"/>
       <c r="L58" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P58" s="2"/>
       <c r="Q58" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="R58" s="2"/>
     </row>
     <row r="59" spans="1:18">
       <c r="A59" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D59" s="2">
         <v>20867</v>
@@ -5374,45 +5388,45 @@
         <v>20867000000.0</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K59" s="2"/>
       <c r="L59" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O59" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P59" s="2"/>
       <c r="Q59" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="R59" s="2"/>
     </row>
     <row r="60" spans="1:18">
       <c r="A60" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D60" s="2">
         <v>799</v>
@@ -5425,45 +5439,45 @@
         <v>799000000.0</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K60" s="2"/>
       <c r="L60" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O60" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P60" s="2"/>
       <c r="Q60" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="R60" s="2"/>
     </row>
     <row r="61" spans="1:18">
       <c r="A61" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D61" s="2">
         <v>22</v>
@@ -5476,45 +5490,45 @@
         <v>22000000.0</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K61" s="2"/>
       <c r="L61" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O61" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P61" s="2"/>
       <c r="Q61" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="R61" s="2"/>
     </row>
     <row r="62" spans="1:18">
       <c r="A62" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D62" s="2">
         <v>269243</v>
@@ -5527,45 +5541,45 @@
         <v>269243000000.0</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K62" s="2"/>
       <c r="L62" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P62" s="2"/>
       <c r="Q62" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="R62" s="2"/>
     </row>
     <row r="63" spans="1:18">
       <c r="A63" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D63" s="2">
         <v>6361</v>
@@ -5578,45 +5592,45 @@
         <v>6361000000.0</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K63" s="2"/>
       <c r="L63" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P63" s="2"/>
       <c r="Q63" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="R63" s="2"/>
     </row>
     <row r="64" spans="1:18">
       <c r="A64" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D64" s="2">
         <v>12</v>
@@ -5629,45 +5643,45 @@
         <v>12000000.0</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K64" s="2"/>
       <c r="L64" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P64" s="2"/>
       <c r="Q64" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="R64" s="2"/>
     </row>
     <row r="65" spans="1:18">
       <c r="A65" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D65" s="2">
         <v>35796</v>
@@ -5680,45 +5694,45 @@
         <v>35796000000.0</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K65" s="2"/>
       <c r="L65" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O65" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P65" s="2"/>
       <c r="Q65" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R65" s="2"/>
     </row>
     <row r="66" spans="1:18">
       <c r="A66" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D66" s="2">
         <v>580775</v>
@@ -5731,45 +5745,45 @@
         <v>580775000000.0</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K66" s="2"/>
       <c r="L66" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O66" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P66" s="2"/>
       <c r="Q66" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="R66" s="2"/>
     </row>
     <row r="67" spans="1:18">
       <c r="A67" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B67" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="D67" s="2">
         <v>522046</v>
@@ -5782,45 +5796,45 @@
         <v>522046000000.0</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K67" s="2"/>
       <c r="L67" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O67" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P67" s="2"/>
       <c r="Q67" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="R67" s="2"/>
     </row>
     <row r="68" spans="1:18">
       <c r="A68" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D68" s="2">
         <v>58729</v>
@@ -5833,45 +5847,45 @@
         <v>58729000000.0</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K68" s="2"/>
       <c r="L68" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O68" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P68" s="2"/>
       <c r="Q68" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R68" s="2"/>
     </row>
     <row r="69" spans="1:18">
       <c r="A69" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D69" s="2">
         <v>54407</v>
@@ -5884,45 +5898,45 @@
         <v>54407000000.0</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K69" s="2"/>
       <c r="L69" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O69" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P69" s="2"/>
       <c r="Q69" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="R69" s="2"/>
     </row>
     <row r="70" spans="1:18">
       <c r="A70" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B70" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="D70" s="2">
         <v>369</v>
@@ -5935,47 +5949,47 @@
         <v>369000000.0</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O70" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P70" s="2"/>
       <c r="Q70" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="R70" s="2"/>
     </row>
     <row r="71" spans="1:18">
       <c r="A71" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D71" s="2">
         <v>-6193</v>
@@ -5988,47 +6002,47 @@
         <v>-6193000000.0</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O71" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P71" s="2"/>
       <c r="Q71" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="R71" s="2"/>
     </row>
     <row r="72" spans="1:18">
       <c r="A72" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D72" s="2">
         <v>-7583</v>
@@ -6041,47 +6055,47 @@
         <v>-7583000000.0</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P72" s="2"/>
       <c r="Q72" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="R72" s="2"/>
     </row>
     <row r="73" spans="1:18">
       <c r="A73" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D73" s="2">
         <v>34</v>
@@ -6094,47 +6108,47 @@
         <v>34000000.0</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O73" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P73" s="2"/>
       <c r="Q73" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="R73" s="2"/>
     </row>
     <row r="74" spans="1:18">
       <c r="A74" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D74" s="2">
         <v>-512</v>
@@ -6147,47 +6161,47 @@
         <v>-512000000.0</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P74" s="2"/>
       <c r="Q74" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="R74" s="2"/>
     </row>
     <row r="75" spans="1:18">
       <c r="A75" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D75" s="2">
         <v>9</v>
@@ -6200,47 +6214,47 @@
         <v>9000000.0</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O75" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P75" s="2"/>
       <c r="Q75" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="R75" s="2"/>
     </row>
     <row r="76" spans="1:18">
       <c r="A76" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D76" s="2">
         <v>5</v>
@@ -6253,47 +6267,47 @@
         <v>5000000.0</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O76" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P76" s="2"/>
       <c r="Q76" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="R76" s="2"/>
     </row>
     <row r="77" spans="1:18">
       <c r="A77" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D77" s="2">
         <v>59</v>
@@ -6306,47 +6320,47 @@
         <v>59000000.0</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O77" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P77" s="2"/>
       <c r="Q77" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="R77" s="2"/>
     </row>
     <row r="78" spans="1:18">
       <c r="A78" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D78" s="2">
         <v>452</v>
@@ -6359,45 +6373,45 @@
         <v>452000000.0</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K78" s="2"/>
       <c r="L78" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O78" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P78" s="2"/>
       <c r="Q78" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="R78" s="2"/>
     </row>
     <row r="79" spans="1:18">
       <c r="A79" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D79" s="2">
         <v>398</v>
@@ -6410,45 +6424,45 @@
         <v>398000000.0</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K79" s="2"/>
       <c r="L79" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O79" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P79" s="2"/>
       <c r="Q79" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="R79" s="2"/>
     </row>
     <row r="80" spans="1:18">
       <c r="A80" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D80" s="2">
         <v>13297</v>
@@ -6461,45 +6475,45 @@
         <v>13297000000.0</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K80" s="2"/>
       <c r="L80" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P80" s="2"/>
       <c r="Q80" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="R80" s="2"/>
     </row>
     <row r="81" spans="1:18">
       <c r="A81" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="D81" s="2">
         <v>13274</v>
@@ -6512,45 +6526,45 @@
         <v>13274000000.0</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K81" s="2"/>
       <c r="L81" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O81" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P81" s="2"/>
       <c r="Q81" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="R81" s="2"/>
     </row>
     <row r="82" spans="1:18">
       <c r="A82" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D82" s="2">
         <v>32</v>
@@ -6563,47 +6577,47 @@
         <v>32000000.0</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O82" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P82" s="2"/>
       <c r="Q82" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="R82" s="2"/>
     </row>
     <row r="83" spans="1:18">
       <c r="A83" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D83" s="2">
         <v>55</v>
@@ -6616,47 +6630,47 @@
         <v>55000000.0</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O83" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P83" s="2"/>
       <c r="Q83" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="R83" s="2"/>
     </row>
     <row r="84" spans="1:18">
       <c r="A84" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D84" s="2">
         <v>1285</v>
@@ -6669,47 +6683,47 @@
         <v>1285000000.0</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O84" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P84" s="2"/>
       <c r="Q84" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="R84" s="2"/>
     </row>
     <row r="85" spans="1:18">
       <c r="A85" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D85" s="2">
         <v>20</v>
@@ -6722,47 +6736,47 @@
         <v>20000000.0</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O85" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P85" s="2"/>
       <c r="Q85" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="R85" s="2"/>
     </row>
     <row r="86" spans="1:18">
       <c r="A86" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D86" s="2">
         <v>13</v>
@@ -6775,47 +6789,47 @@
         <v>13000000.0</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O86" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P86" s="2"/>
       <c r="Q86" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="R86" s="2"/>
     </row>
     <row r="87" spans="1:18">
       <c r="A87" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D87" s="2">
         <v>810</v>
@@ -6828,47 +6842,47 @@
         <v>810000000.0</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O87" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P87" s="2"/>
       <c r="Q87" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="R87" s="2"/>
     </row>
     <row r="88" spans="1:18">
       <c r="A88" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D88" s="2">
         <v>60</v>
@@ -6881,47 +6895,47 @@
         <v>60000000.0</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O88" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P88" s="2"/>
       <c r="Q88" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="R88" s="2"/>
     </row>
     <row r="89" spans="1:18">
       <c r="A89" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D89" s="2">
         <v>59</v>
@@ -6934,47 +6948,47 @@
         <v>59000000.0</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O89" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P89" s="2"/>
       <c r="Q89" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R89" s="2"/>
     </row>
     <row r="90" spans="1:18">
       <c r="A90" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D90" s="2">
         <v>701</v>
@@ -6987,47 +7001,47 @@
         <v>701000000.0</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O90" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P90" s="2"/>
       <c r="Q90" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R90" s="2"/>
     </row>
     <row r="91" spans="1:18">
       <c r="A91" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D91" s="2">
         <v>3860</v>
@@ -7040,45 +7054,45 @@
         <v>3860000000.0</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K91" s="2"/>
       <c r="L91" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O91" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P91" s="2"/>
       <c r="Q91" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="R91" s="2"/>
     </row>
     <row r="92" spans="1:18">
       <c r="A92" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D92" s="2">
         <v>4341</v>
@@ -7091,45 +7105,45 @@
         <v>4341000000.0</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K92" s="2"/>
       <c r="L92" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O92" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P92" s="2"/>
       <c r="Q92" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R92" s="2"/>
     </row>
     <row r="93" spans="1:18">
       <c r="A93" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D93" s="2">
         <v>3424</v>
@@ -7142,45 +7156,45 @@
         <v>3424000000.0</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K93" s="2"/>
       <c r="L93" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O93" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P93" s="2"/>
       <c r="Q93" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="R93" s="2"/>
     </row>
     <row r="94" spans="1:18">
       <c r="A94" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B94" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="D94" s="2">
         <v>5285</v>
@@ -7193,45 +7207,45 @@
         <v>5285000000.0</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K94" s="2"/>
       <c r="L94" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O94" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P94" s="2"/>
       <c r="Q94" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="R94" s="2"/>
     </row>
     <row r="95" spans="1:18">
       <c r="A95" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D95" s="2">
         <v>2870</v>
@@ -7244,33 +7258,33 @@
         <v>2870000000.0</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K95" s="2"/>
       <c r="L95" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O95" s="2" t="s">
         <v>11</v>
       </c>
       <c r="P95" s="2"/>
       <c r="Q95" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="R95" s="2"/>
     </row>
@@ -7289,7 +7303,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="3" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="44.7109375" customWidth="1"/>
     <col min="4" max="5" width="24.7109375" customWidth="1"/>
     <col min="6" max="6" width="13.7109375" customWidth="1"/>
     <col min="7" max="7" width="18.7109375" customWidth="1"/>
@@ -7304,67 +7319,67 @@
   <sheetData>
     <row r="1" spans="1:15" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D2" s="3">
         <f>IF(OR('Facts'!F3&lt;=0,'Facts'!F2&lt;0),NA(),((('Facts'!F2-'Facts'!F3)/'Facts'!F3))*1)</f>
         <v>0.3689034936008302</v>
       </c>
       <c r="E2" s="4">
-        <f>D2/K2</f>
+        <f>D2</f>
         <v>0.3689034936008302</v>
       </c>
       <c r="F2" s="2" t="str">
@@ -7376,46 +7391,46 @@
         <v/>
       </c>
       <c r="H2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K2" s="2">
         <v>1</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D3" s="3">
         <f>IF(OR('Facts'!F13&lt;=0,'Facts'!F12&lt;0),NA(),((('Facts'!F12-'Facts'!F13)/'Facts'!F13))*1)</f>
         <v>0.3559103002660585</v>
       </c>
       <c r="E3" s="4">
-        <f>D3/K3</f>
+        <f>D3</f>
         <v>0.3559103002660585</v>
       </c>
       <c r="F3" s="2" t="str">
@@ -7427,46 +7442,46 @@
         <v/>
       </c>
       <c r="H3" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K3" s="2">
         <v>1</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D4" s="3">
         <f>IF(OR('Facts'!F9&lt;=0,'Facts'!F8&lt;0),NA(),((('Facts'!F8-'Facts'!F9)/'Facts'!F9))*1)</f>
         <v>0.42449336834309565</v>
       </c>
       <c r="E4" s="4">
-        <f>D4/K4</f>
+        <f>D4</f>
         <v>0.42449336834309565</v>
       </c>
       <c r="F4" s="2" t="str">
@@ -7478,46 +7493,46 @@
         <v/>
       </c>
       <c r="H4" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K4" s="2">
         <v>1</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D5" s="3">
         <f>IF(OR('Facts'!F7&lt;=0,'Facts'!F6&lt;0),NA(),((('Facts'!F6-'Facts'!F7)/'Facts'!F7))*1)</f>
         <v>0.037345240511467426</v>
       </c>
       <c r="E5" s="4">
-        <f>D5/K5</f>
+        <f>D5</f>
         <v>0.037345240511467426</v>
       </c>
       <c r="F5" s="2" t="str">
@@ -7529,39 +7544,39 @@
         <v/>
       </c>
       <c r="H5" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D6" s="3">
         <f>(('Facts'!F2-'Facts'!F3))*1</f>
@@ -7580,39 +7595,39 @@
         <v/>
       </c>
       <c r="H6" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K6" s="2">
         <v>1000000</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D7" s="3">
         <f>(('Facts'!F4-'Facts'!F5))*1</f>
@@ -7631,46 +7646,46 @@
         <v/>
       </c>
       <c r="H7" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K7" s="2">
         <v>1000000</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D8" s="3">
         <f>IF('Calculations'!D7&lt;=0,NA(),(('Calculations'!D6/'Calculations'!D7))*1)</f>
         <v>0.942831884485045</v>
       </c>
       <c r="E8" s="4">
-        <f>D8/K8</f>
+        <f>D8</f>
         <v>0.942831884485045</v>
       </c>
       <c r="F8" s="2" t="str">
@@ -7682,39 +7697,39 @@
         <v/>
       </c>
       <c r="H8" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K8" s="2">
         <v>1</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D9" s="3">
         <f>(('Facts'!F14-'Facts'!F15))*1</f>
@@ -7733,39 +7748,39 @@
         <v/>
       </c>
       <c r="H9" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K9" s="2">
         <v>1000000</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D10" s="3">
         <f>(('Facts'!F16-'Facts'!F17))*1</f>
@@ -7784,46 +7799,46 @@
         <v/>
       </c>
       <c r="H10" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K10" s="2">
         <v>1000000</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D11" s="3">
         <f>IF('Calculations'!D10&lt;=0,NA(),(('Calculations'!D9/'Calculations'!D10))*1)</f>
         <v>0.8026093630084421</v>
       </c>
       <c r="E11" s="4">
-        <f>D11/K11</f>
+        <f>D11</f>
         <v>0.8026093630084421</v>
       </c>
       <c r="F11" s="2" t="str">
@@ -7835,39 +7850,39 @@
         <v/>
       </c>
       <c r="H11" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D12" s="3">
         <f>(('Facts'!F8*1)+('Facts'!F18*1)+('Facts'!F19*1)+('Facts'!F20*1)+('Facts'!F21*1)+('Facts'!F22*1)+('Facts'!F23*1)+('Facts'!F24*1)+('Facts'!F25*1)+('Facts'!F26*1)+('Facts'!F27*1)+('Facts'!F28*1)+('Facts'!F29*1)+('Facts'!F30*1)+('Facts'!F31*1)+('Facts'!F32*1)+('Facts'!F33*1)+('Facts'!F34*1))*1</f>
@@ -7886,39 +7901,39 @@
         <v/>
       </c>
       <c r="H12" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K12" s="2">
         <v>1000000</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D13" s="3">
         <f>(('Calculations'!D12*1)+('Facts'!F36*1)+('Facts'!F37*1)+('Facts'!F38*1)+('Facts'!F39*1))*1</f>
@@ -7937,39 +7952,39 @@
         <v/>
       </c>
       <c r="H13" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K13" s="2">
         <v>1000000</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D14" s="3">
         <f>(('Calculations'!D13*1)+('Facts'!F41*1))*1</f>
@@ -7988,39 +8003,39 @@
         <v/>
       </c>
       <c r="H14" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K14" s="2">
         <v>1000000</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D15" s="3">
         <f>(('Facts'!F49*1)+('Facts'!F42*1)+('Facts'!F43*1)+('Facts'!F44*1)+('Facts'!F45*1))*1</f>
@@ -8039,39 +8054,39 @@
         <v/>
       </c>
       <c r="H15" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K15" s="2">
         <v>1000000</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D16" s="3">
         <f>(('Facts'!F52*1)+('Facts'!F53*1)+('Facts'!F54*1)+('Facts'!F55*1))*1</f>
@@ -8090,37 +8105,37 @@
         <v/>
       </c>
       <c r="H16" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K16" s="2">
         <v>1000000</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D17" s="3">
         <f>(('Facts'!F53-'Facts'!F56))*1</f>
@@ -8139,37 +8154,37 @@
         <v/>
       </c>
       <c r="H17" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K17" s="2">
         <v>1000000</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D18" s="3">
         <f>(('Facts'!F54*1)+('Facts'!F57*1)+('Facts'!F58*1)+('Facts'!F59*1)+('Facts'!F60*1)+('Facts'!F61*1))*1</f>
@@ -8188,37 +8203,37 @@
         <v/>
       </c>
       <c r="H18" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K18" s="2">
         <v>1000000</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D19" s="3">
         <f>(('Facts'!F55*1)+('Facts'!F63*1)+('Facts'!F64*-1))*1</f>
@@ -8237,37 +8252,37 @@
         <v/>
       </c>
       <c r="H19" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K19" s="2">
         <v>1000000</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D20" s="3">
         <f>(('Facts'!F66-'Facts'!F67))*1</f>
@@ -8286,37 +8301,37 @@
         <v/>
       </c>
       <c r="H20" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K20" s="2">
         <v>1000000</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D21" s="3">
         <f>(('Facts'!F69*1)+('Facts'!F12*1)+('Facts'!F70*1)+('Facts'!F71*1)+('Facts'!F72*1)+('Facts'!F73*1)+('Facts'!F74*1)+('Facts'!F23*1)+('Facts'!F75*1))*1</f>
@@ -8335,39 +8350,39 @@
         <v/>
       </c>
       <c r="H21" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K21" s="2">
         <v>1000000</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D22" s="3">
         <f>(('Facts'!F78*1)+('Facts'!F76*1)+('Facts'!F77*-1))*1</f>
@@ -8386,39 +8401,39 @@
         <v/>
       </c>
       <c r="H22" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K22" s="2">
         <v>1000000</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D23" s="3">
         <f>(('Facts'!F80*1)+('Facts'!F82*1)+('Facts'!F83*-1))*1</f>
@@ -8437,39 +8452,39 @@
         <v/>
       </c>
       <c r="H23" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K23" s="2">
         <v>1000000</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D24" s="3">
         <f>(('Facts'!F91*1)+('Facts'!F84*1)+('Facts'!F85*1)+('Facts'!F86*-1)+('Facts'!F87*-1)+('Facts'!F88*-1)+('Facts'!F89*1))*1</f>
@@ -8488,39 +8503,39 @@
         <v/>
       </c>
       <c r="H24" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K24" s="2">
         <v>1000000</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D25" s="3">
         <f>(('Facts'!F40*1)+('Facts'!F46*-1)+('Facts'!F47*-1))*1</f>
@@ -8539,39 +8554,39 @@
         <v/>
       </c>
       <c r="H25" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K25" s="2">
         <v>1000000</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D26" s="3">
         <f>(('Calculations'!D25-'Facts'!F48))*1</f>
@@ -8590,46 +8605,46 @@
         <v/>
       </c>
       <c r="H26" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K26" s="2">
         <v>1000000</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D27" s="3">
         <f>IF('Facts'!F8&lt;=0,NA(),(('Facts'!F10/'Facts'!F8))*1)</f>
         <v>0.1569619056621609</v>
       </c>
       <c r="E27" s="4">
-        <f>D27/K27</f>
+        <f>D27</f>
         <v>0.1569619056621609</v>
       </c>
       <c r="F27" s="2" t="str">
@@ -8641,39 +8656,39 @@
         <v/>
       </c>
       <c r="H27" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K27" s="2">
         <v>1</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D28" s="3">
         <f>(('Facts'!F10-'Facts'!F11))*1</f>
@@ -8692,46 +8707,46 @@
         <v/>
       </c>
       <c r="H28" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K28" s="2">
         <v>1000000</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D29" s="3">
         <f>IF('Calculations'!D28&lt;=0,NA(),(('Facts'!F90/'Calculations'!D28))*1)</f>
         <v>0.4319162045594578</v>
       </c>
       <c r="E29" s="4">
-        <f>D29/K29</f>
+        <f>D29</f>
         <v>0.4319162045594578</v>
       </c>
       <c r="F29" s="2" t="str">
@@ -8743,28 +8758,28 @@
         <v/>
       </c>
       <c r="H29" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K29" s="2">
         <v>1</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -8794,50 +8809,50 @@
   <sheetData>
     <row r="1" spans="1:10" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="33" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E2" s="3">
+        <v>121</v>
+      </c>
+      <c r="E2" s="2">
         <f>ROUND('Calculations'!D12-'Facts'!F35,J2)</f>
         <v>0.0</v>
       </c>
@@ -8849,7 +8864,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I2" s="2">
         <f>IF(ISNUMBER(E2),"","missing or unavailable input")</f>
@@ -8859,20 +8874,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" ht="33" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E3" s="3">
+        <v>131</v>
+      </c>
+      <c r="E3" s="2">
         <f>ROUND('Calculations'!D13-'Facts'!F40,J3)</f>
         <v>0.0</v>
       </c>
@@ -8884,7 +8899,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I3" s="2">
         <f>IF(ISNUMBER(E3),"","missing or unavailable input")</f>
@@ -8894,20 +8909,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" ht="33" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E4" s="3">
+        <v>135</v>
+      </c>
+      <c r="E4" s="2">
         <f>ROUND('Calculations'!D14-'Facts'!F42,J4)</f>
         <v>0.0</v>
       </c>
@@ -8919,7 +8934,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I4" s="2">
         <f>IF(ISNUMBER(E4),"","missing or unavailable input")</f>
@@ -8929,20 +8944,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" ht="33" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E5" s="3">
+        <v>153</v>
+      </c>
+      <c r="E5" s="2">
         <f>ROUND('Calculations'!D15-'Facts'!F50,J5)</f>
         <v>0.0</v>
       </c>
@@ -8954,7 +8969,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I5" s="2">
         <f>IF(ISNUMBER(E5),"","missing or unavailable input")</f>
@@ -8964,20 +8979,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" ht="33" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E6" s="3">
+        <v>155</v>
+      </c>
+      <c r="E6" s="2">
         <f>ROUND('Calculations'!D16-'Facts'!F51,J6)</f>
         <v>0.0</v>
       </c>
@@ -8989,7 +9004,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I6" s="2">
         <f>IF(ISNUMBER(E6),"","missing or unavailable input")</f>
@@ -8999,20 +9014,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" ht="33" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E7" s="3">
+        <v>153</v>
+      </c>
+      <c r="E7" s="2">
         <f>ROUND('Calculations'!D17-'Facts'!F50,J7)</f>
         <v>0.0</v>
       </c>
@@ -9024,7 +9039,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I7" s="2">
         <f>IF(ISNUMBER(E7),"","missing or unavailable input")</f>
@@ -9034,20 +9049,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" ht="33" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E8" s="3">
+        <v>178</v>
+      </c>
+      <c r="E8" s="2">
         <f>ROUND('Calculations'!D18-'Facts'!F62,J8)</f>
         <v>0.0</v>
       </c>
@@ -9059,7 +9074,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I8" s="2">
         <f>IF(ISNUMBER(E8),"","missing or unavailable input")</f>
@@ -9069,20 +9084,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" ht="33" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E9" s="3">
+        <v>184</v>
+      </c>
+      <c r="E9" s="2">
         <f>ROUND('Calculations'!D19-'Facts'!F65,J9)</f>
         <v>0.0</v>
       </c>
@@ -9094,7 +9109,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I9" s="2">
         <f>IF(ISNUMBER(E9),"","missing or unavailable input")</f>
@@ -9104,20 +9119,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" ht="33" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E10" s="3">
+        <v>191</v>
+      </c>
+      <c r="E10" s="2">
         <f>ROUND('Calculations'!D20-'Facts'!F68,J10)</f>
         <v>0.0</v>
       </c>
@@ -9129,7 +9144,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I10" s="2">
         <f>IF(ISNUMBER(E10),"","missing or unavailable input")</f>
@@ -9139,20 +9154,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="33" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E11" s="3">
+        <v>191</v>
+      </c>
+      <c r="E11" s="2">
         <f>ROUND('Calculations'!D21-'Facts'!F68,J11)</f>
         <v>0.0</v>
       </c>
@@ -9164,7 +9179,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I11" s="2">
         <f>IF(ISNUMBER(E11),"","missing or unavailable input")</f>
@@ -9174,20 +9189,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="33" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E12" s="3">
+        <v>215</v>
+      </c>
+      <c r="E12" s="2">
         <f>ROUND('Calculations'!D22-'Facts'!F79,J12)</f>
         <v>0.0</v>
       </c>
@@ -9199,7 +9214,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I12" s="2">
         <f>IF(ISNUMBER(E12),"","missing or unavailable input")</f>
@@ -9209,20 +9224,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="33" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E13" s="3">
+        <v>220</v>
+      </c>
+      <c r="E13" s="2">
         <f>ROUND('Calculations'!D23-'Facts'!F81,J13)</f>
         <v>0.0</v>
       </c>
@@ -9234,7 +9249,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I13" s="2">
         <f>IF(ISNUMBER(E13),"","missing or unavailable input")</f>
@@ -9244,20 +9259,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="33" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E14" s="3">
+        <v>243</v>
+      </c>
+      <c r="E14" s="2">
         <f>ROUND('Calculations'!D24-'Facts'!F92,J14)</f>
         <v>0.0</v>
       </c>
@@ -9269,7 +9284,7 @@
         <v>within_input_tolerance</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I14" s="2">
         <f>IF(ISNUMBER(E14),"","missing or unavailable input")</f>
@@ -9300,82 +9315,82 @@
   <sheetData>
     <row r="1" spans="1:6" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -9397,274 +9412,274 @@
   <sheetData>
     <row r="1" spans="1:5" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>426</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -9689,282 +9704,282 @@
   <sheetData>
     <row r="1" spans="1:9" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
   </sheetData>
@@ -9983,162 +9998,162 @@
   <sheetData>
     <row r="1" spans="1:10" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>548</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>
@@ -10161,102 +10176,102 @@
   <sheetData>
     <row r="1" spans="1:6" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
   </sheetData>
